--- a/data/trans_camb/P20B-Clase-trans_camb.xlsx
+++ b/data/trans_camb/P20B-Clase-trans_camb.xlsx
@@ -677,47 +677,47 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>-28,5; 29,98</t>
+          <t>-32,9; 28,2</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>-22,06; 31,47</t>
+          <t>-22,96; 30,13</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>-15,88; 35,29</t>
+          <t>-14,01; 37,06</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>-12,0; 33,56</t>
+          <t>-9,44; 33,1</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>-27,24; 8,79</t>
+          <t>-30,4; 9,42</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>-27,21; 10,07</t>
+          <t>-25,97; 8,98</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>-16,53; 22,24</t>
+          <t>-16,04; 21,19</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>-20,83; 13,49</t>
+          <t>-21,44; 13,07</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>-13,78; 18,28</t>
+          <t>-15,71; 17,97</t>
         </is>
       </c>
     </row>
@@ -783,22 +783,22 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>-71,45; 198,14</t>
+          <t>-79,58; 163,02</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>-57,68; 180,43</t>
+          <t>-53,58; 169,24</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>-35,48; 215,35</t>
+          <t>-31,62; 251,27</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>-59,91; —</t>
+          <t>-51,0; inf</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -808,22 +808,22 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>-88,62; 375,19</t>
+          <t>-87,18; 239,0</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>-47,86; 174,12</t>
+          <t>-50,3; 154,23</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>-64,77; 99,43</t>
+          <t>-64,66; 89,44</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>-42,22; 139,82</t>
+          <t>-42,85; 126,03</t>
         </is>
       </c>
     </row>
@@ -893,47 +893,47 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>-33,65; 13,57</t>
+          <t>-34,57; 15,28</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>-24,3; 26,05</t>
+          <t>-25,82; 26,08</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>-14,81; 37,89</t>
+          <t>-13,34; 41,1</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>-18,32; 17,39</t>
+          <t>-18,19; 16,26</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>-9,89; 34,29</t>
+          <t>-8,9; 31,9</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>-6,22; 31,66</t>
+          <t>-5,82; 32,92</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>-18,07; 9,86</t>
+          <t>-18,53; 10,59</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>-7,94; 25,25</t>
+          <t>-8,12; 24,22</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>-1,67; 29,57</t>
+          <t>-1,25; 29,39</t>
         </is>
       </c>
     </row>
@@ -1004,42 +1004,42 @@
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>-81,83; 527,14</t>
+          <t>-87,59; 625,41</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>-52,11; 587,45</t>
+          <t>-47,95; inf</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>-81,68; 455,29</t>
+          <t>-86,32; 390,49</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>-50,29; 708,32</t>
+          <t>-45,96; 607,17</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>-39,42; 705,05</t>
+          <t>-37,3; 546,58</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>-79,56; 127,61</t>
+          <t>-77,56; 157,23</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>-44,04; 304,89</t>
+          <t>-41,77; 370,11</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>-13,97; 365,24</t>
+          <t>-12,63; 416,75</t>
         </is>
       </c>
     </row>
@@ -1109,47 +1109,47 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>-33,34; 16,94</t>
+          <t>-33,62; 15,01</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>-30,06; 23,53</t>
+          <t>-33,89; 23,15</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>-20,48; 32,11</t>
+          <t>-18,69; 32,94</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>-17,17; 36,84</t>
+          <t>-16,69; 36,55</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>-5,1; 59,15</t>
+          <t>-7,19; 58,28</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>-15,64; 36,95</t>
+          <t>-16,52; 36,28</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>-17,95; 19,54</t>
+          <t>-19,29; 18,98</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>-10,82; 29,31</t>
+          <t>-12,84; 30,37</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>-7,79; 29,76</t>
+          <t>-7,31; 30,43</t>
         </is>
       </c>
     </row>
@@ -1215,47 +1215,47 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>-63,98; 89,78</t>
+          <t>-61,79; 67,29</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>-56,45; 110,55</t>
+          <t>-61,99; 116,4</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>-36,81; 160,77</t>
+          <t>-39,21; 154,61</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>-59,95; —</t>
+          <t>-60,42; —</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>-32,37; 1075,56</t>
+          <t>-35,51; 1128,21</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>-61,17; 731,19</t>
+          <t>-59,41; 1275,76</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>-45,58; 107,65</t>
+          <t>-46,44; 118,04</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>-31,16; 185,57</t>
+          <t>-33,11; 189,73</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>-22,79; 176,42</t>
+          <t>-19,71; 182,38</t>
         </is>
       </c>
     </row>
@@ -1325,47 +1325,47 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>-6,82; 24,19</t>
+          <t>-6,06; 24,88</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>-1,16; 34,62</t>
+          <t>1,25; 35,89</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>-12,46; 17,25</t>
+          <t>-11,97; 17,68</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>-13,16; 12,44</t>
+          <t>-12,3; 12,51</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>-13,39; 13,47</t>
+          <t>-14,13; 13,15</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>-15,06; 10,76</t>
+          <t>-15,19; 10,71</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>-5,22; 13,95</t>
+          <t>-5,85; 14,53</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>-3,02; 18,08</t>
+          <t>-2,83; 19,32</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>-10,02; 10,03</t>
+          <t>-10,13; 10,43</t>
         </is>
       </c>
     </row>
@@ -1431,47 +1431,47 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>-22,1; 185,87</t>
+          <t>-22,08; 175,84</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>-5,38; 268,6</t>
+          <t>2,71; 251,18</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>-42,29; 134,51</t>
+          <t>-43,1; 121,17</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>-53,03; 104,29</t>
+          <t>-50,06; 111,34</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>-50,82; 117,2</t>
+          <t>-51,98; 100,39</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>-58,8; 91,28</t>
+          <t>-57,6; 95,39</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>-21,47; 92,64</t>
+          <t>-23,35; 95,91</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
         <is>
-          <t>-11,35; 121,93</t>
+          <t>-13,62; 113,63</t>
         </is>
       </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>-38,31; 64,78</t>
+          <t>-41,04; 69,81</t>
         </is>
       </c>
     </row>
@@ -1541,47 +1541,47 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>-22,45; 32,16</t>
+          <t>-23,21; 31,97</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>-22,87; 36,29</t>
+          <t>-20,66; 36,57</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>-25,51; 26,21</t>
+          <t>-25,88; 28,3</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>-4,43; 31,95</t>
+          <t>-2,5; 29,71</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>-1,45; 38,49</t>
+          <t>-1,85; 38,54</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>-6,66; 27,87</t>
+          <t>-5,72; 26,27</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>-3,08; 24,36</t>
+          <t>-5,36; 24,84</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
         <is>
-          <t>-2,96; 31,5</t>
+          <t>-1,35; 31,23</t>
         </is>
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>-7,44; 21,71</t>
+          <t>-7,17; 21,33</t>
         </is>
       </c>
     </row>
@@ -1647,47 +1647,47 @@
       </c>
       <c r="C23" s="2" t="inlineStr">
         <is>
-          <t>-47,88; 273,85</t>
+          <t>-51,47; 263,35</t>
         </is>
       </c>
       <c r="D23" s="2" t="inlineStr">
         <is>
-          <t>-55,07; 288,75</t>
+          <t>-45,61; 319,32</t>
         </is>
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>-52,33; 225,69</t>
+          <t>-54,89; 244,26</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>-14,39; 282,72</t>
+          <t>-10,11; 251,59</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
         <is>
-          <t>-8,09; 296,71</t>
+          <t>-6,36; 343,65</t>
         </is>
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>-20,92; 248,92</t>
+          <t>-21,15; 203,97</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>-9,51; 164,97</t>
+          <t>-17,09; 150,7</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
         <is>
-          <t>-9,83; 196,64</t>
+          <t>-8,74; 199,35</t>
         </is>
       </c>
       <c r="K23" s="2" t="inlineStr">
         <is>
-          <t>-22,58; 142,86</t>
+          <t>-20,61; 130,2</t>
         </is>
       </c>
     </row>
@@ -1757,47 +1757,47 @@
       </c>
       <c r="C25" s="2" t="inlineStr">
         <is>
-          <t>-47,29; 63,85</t>
+          <t>-53,74; 63,38</t>
         </is>
       </c>
       <c r="D25" s="2" t="inlineStr">
         <is>
-          <t>-88,0; 24,53</t>
+          <t>-87,78; 24,62</t>
         </is>
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>-100,0; 55,12</t>
+          <t>-87,03; 56,5</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>-15,74; 11,7</t>
+          <t>-13,42; 13,21</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
         <is>
-          <t>-15,61; 12,64</t>
+          <t>-15,62; 11,51</t>
         </is>
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>-15,28; 21,47</t>
+          <t>-15,63; 20,21</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>-12,52; 13,74</t>
+          <t>-12,24; 11,93</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
         <is>
-          <t>-16,75; 10,91</t>
+          <t>-17,36; 10,35</t>
         </is>
       </c>
       <c r="K25" s="2" t="inlineStr">
         <is>
-          <t>-14,57; 20,56</t>
+          <t>-15,13; 19,83</t>
         </is>
       </c>
     </row>
@@ -1878,32 +1878,32 @@
       </c>
       <c r="F27" s="2" t="inlineStr">
         <is>
-          <t>-52,06; 68,67</t>
+          <t>-43,82; 72,79</t>
         </is>
       </c>
       <c r="G27" s="2" t="inlineStr">
         <is>
-          <t>-53,95; 69,23</t>
+          <t>-56,45; 62,16</t>
         </is>
       </c>
       <c r="H27" s="2" t="inlineStr">
         <is>
-          <t>-53,83; 126,43</t>
+          <t>-55,3; 115,67</t>
         </is>
       </c>
       <c r="I27" s="2" t="inlineStr">
         <is>
-          <t>-40,87; 78,34</t>
+          <t>-41,22; 63,59</t>
         </is>
       </c>
       <c r="J27" s="2" t="inlineStr">
         <is>
-          <t>-55,23; 65,37</t>
+          <t>-57,94; 56,42</t>
         </is>
       </c>
       <c r="K27" s="2" t="inlineStr">
         <is>
-          <t>-49,89; 114,66</t>
+          <t>-54,24; 105,78</t>
         </is>
       </c>
     </row>
@@ -1973,47 +1973,47 @@
       </c>
       <c r="C29" s="2" t="inlineStr">
         <is>
-          <t>-6,27; 14,49</t>
+          <t>-5,58; 14,02</t>
         </is>
       </c>
       <c r="D29" s="2" t="inlineStr">
         <is>
-          <t>-2,81; 17,68</t>
+          <t>-3,07; 17,54</t>
         </is>
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>-2,15; 17,61</t>
+          <t>-4,21; 16,82</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>-2,48; 11,36</t>
+          <t>-3,3; 11,05</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
         <is>
-          <t>-3,16; 11,06</t>
+          <t>-3,43; 12,17</t>
         </is>
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>-4,18; 10,57</t>
+          <t>-4,53; 10,06</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>-1,44; 10,08</t>
+          <t>-2,01; 10,3</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
         <is>
-          <t>-1,01; 11,73</t>
+          <t>-0,33; 11,75</t>
         </is>
       </c>
       <c r="K29" s="2" t="inlineStr">
         <is>
-          <t>-0,62; 11,14</t>
+          <t>-0,61; 11,7</t>
         </is>
       </c>
     </row>
@@ -2079,47 +2079,47 @@
       </c>
       <c r="C31" s="2" t="inlineStr">
         <is>
-          <t>-20,27; 72,99</t>
+          <t>-19,47; 68,31</t>
         </is>
       </c>
       <c r="D31" s="2" t="inlineStr">
         <is>
-          <t>-9,03; 80,31</t>
+          <t>-9,57; 86,94</t>
         </is>
       </c>
       <c r="E31" s="2" t="inlineStr">
         <is>
-          <t>-7,39; 88,49</t>
+          <t>-14,42; 85,47</t>
         </is>
       </c>
       <c r="F31" s="2" t="inlineStr">
         <is>
-          <t>-10,87; 67,44</t>
+          <t>-13,55; 65,91</t>
         </is>
       </c>
       <c r="G31" s="2" t="inlineStr">
         <is>
-          <t>-14,03; 67,62</t>
+          <t>-15,11; 75,03</t>
         </is>
       </c>
       <c r="H31" s="2" t="inlineStr">
         <is>
-          <t>-17,95; 65,72</t>
+          <t>-18,14; 60,03</t>
         </is>
       </c>
       <c r="I31" s="2" t="inlineStr">
         <is>
-          <t>-5,7; 54,18</t>
+          <t>-7,69; 50,51</t>
         </is>
       </c>
       <c r="J31" s="2" t="inlineStr">
         <is>
-          <t>-3,63; 60,56</t>
+          <t>-0,99; 61,44</t>
         </is>
       </c>
       <c r="K31" s="2" t="inlineStr">
         <is>
-          <t>-2,8; 57,63</t>
+          <t>-2,24; 62,54</t>
         </is>
       </c>
     </row>

--- a/data/trans_camb/P20B-Clase-trans_camb.xlsx
+++ b/data/trans_camb/P20B-Clase-trans_camb.xlsx
@@ -634,7 +634,7 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>11,9</t>
+          <t>11,61</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
@@ -649,7 +649,7 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>-4,8</t>
+          <t>-4,59</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
@@ -664,7 +664,7 @@
       </c>
       <c r="K4" s="2" t="inlineStr">
         <is>
-          <t>2,63</t>
+          <t>1,82</t>
         </is>
       </c>
     </row>
@@ -677,47 +677,47 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>-32,9; 28,2</t>
+          <t>-28,39; 28,31</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>-22,96; 30,13</t>
+          <t>-22,0; 34,4</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>-14,01; 37,06</t>
+          <t>-16,58; 34,09</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>-9,44; 33,1</t>
+          <t>-13,66; 32,62</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>-30,4; 9,42</t>
+          <t>-27,7; 7,9</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>-25,97; 8,98</t>
+          <t>-26,61; 10,73</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>-16,04; 21,19</t>
+          <t>-13,53; 21,89</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>-21,44; 13,07</t>
+          <t>-19,67; 14,47</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>-15,71; 17,97</t>
+          <t>-15,36; 18,12</t>
         </is>
       </c>
     </row>
@@ -740,7 +740,7 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>38,49%</t>
+          <t>37,55%</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
@@ -755,7 +755,7 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>-32,01%</t>
+          <t>-30,65%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
@@ -770,7 +770,7 @@
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>11,05%</t>
+          <t>7,65%</t>
         </is>
       </c>
     </row>
@@ -783,22 +783,22 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>-79,58; 163,02</t>
+          <t>-72,72; 229,59</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>-53,58; 169,24</t>
+          <t>-55,01; 204,63</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>-31,62; 251,27</t>
+          <t>-36,74; 234,51</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>-51,0; inf</t>
+          <t>-60,81; 790,76</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -808,22 +808,22 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>-87,18; 239,0</t>
+          <t>-86,17; —</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>-50,3; 154,23</t>
+          <t>-42,16; 157,62</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>-64,66; 89,44</t>
+          <t>-59,69; 110,36</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>-42,85; 126,03</t>
+          <t>-46,02; 144,28</t>
         </is>
       </c>
     </row>
@@ -850,7 +850,7 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>13,36</t>
+          <t>14,56</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
@@ -865,7 +865,7 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>13,84</t>
+          <t>15,65</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
@@ -880,7 +880,7 @@
       </c>
       <c r="K8" s="2" t="inlineStr">
         <is>
-          <t>14,02</t>
+          <t>15,52</t>
         </is>
       </c>
     </row>
@@ -893,47 +893,47 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>-34,57; 15,28</t>
+          <t>-35,7; 11,66</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>-25,82; 26,08</t>
+          <t>-25,16; 26,55</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>-13,34; 41,1</t>
+          <t>-13,3; 40,79</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>-18,19; 16,26</t>
+          <t>-19,02; 16,57</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>-8,9; 31,9</t>
+          <t>-7,99; 34,01</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>-5,82; 32,92</t>
+          <t>-2,86; 32,94</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>-18,53; 10,59</t>
+          <t>-17,31; 11,06</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>-8,12; 24,22</t>
+          <t>-8,92; 23,94</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>-1,25; 29,39</t>
+          <t>-0,5; 30,55</t>
         </is>
       </c>
     </row>
@@ -956,7 +956,7 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>72,92%</t>
+          <t>79,43%</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
@@ -971,7 +971,7 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>99,91%</t>
+          <t>112,98%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
@@ -986,7 +986,7 @@
       </c>
       <c r="K10" s="2" t="inlineStr">
         <is>
-          <t>91,14%</t>
+          <t>100,84%</t>
         </is>
       </c>
     </row>
@@ -1004,42 +1004,42 @@
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>-87,59; 625,41</t>
+          <t>-77,16; —</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>-47,95; inf</t>
+          <t>-48,37; 860,78</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>-86,32; 390,49</t>
+          <t>-83,57; 298,27</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>-45,96; 607,17</t>
+          <t>-46,75; 852,86</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>-37,3; 546,58</t>
+          <t>-26,05; 755,76</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>-77,56; 157,23</t>
+          <t>-77,67; 153,86</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>-41,77; 370,11</t>
+          <t>-40,28; 331,45</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>-12,63; 416,75</t>
+          <t>-10,63; 367,65</t>
         </is>
       </c>
     </row>
@@ -1066,7 +1066,7 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>7,37</t>
+          <t>9,98</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
@@ -1081,7 +1081,7 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>10,81</t>
+          <t>8,73</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
@@ -1096,7 +1096,7 @@
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>11,09</t>
+          <t>12,13</t>
         </is>
       </c>
     </row>
@@ -1109,47 +1109,47 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>-33,62; 15,01</t>
+          <t>-33,82; 16,71</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>-33,89; 23,15</t>
+          <t>-29,2; 24,98</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>-18,69; 32,94</t>
+          <t>-17,8; 34,75</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>-16,69; 36,55</t>
+          <t>-15,54; 36,65</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>-7,19; 58,28</t>
+          <t>-8,39; 56,36</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>-16,52; 36,28</t>
+          <t>-18,41; 31,01</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>-19,29; 18,98</t>
+          <t>-16,84; 19,53</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>-12,84; 30,37</t>
+          <t>-12,73; 28,6</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>-7,31; 30,43</t>
+          <t>-6,87; 32,01</t>
         </is>
       </c>
     </row>
@@ -1172,7 +1172,7 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>19,47%</t>
+          <t>26,37%</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
@@ -1187,7 +1187,7 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>63,82%</t>
+          <t>51,51%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
@@ -1202,7 +1202,7 @@
       </c>
       <c r="K14" s="2" t="inlineStr">
         <is>
-          <t>39,14%</t>
+          <t>42,8%</t>
         </is>
       </c>
     </row>
@@ -1215,47 +1215,47 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>-61,79; 67,29</t>
+          <t>-61,59; 87,82</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>-61,99; 116,4</t>
+          <t>-56,91; 137,03</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>-39,21; 154,61</t>
+          <t>-33,01; 153,58</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>-60,42; —</t>
+          <t>-61,2; 864,47</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>-35,51; 1128,21</t>
+          <t>-38,71; 1022,65</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>-59,41; 1275,76</t>
+          <t>-65,88; 517,69</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>-46,44; 118,04</t>
+          <t>-44,1; 110,46</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>-33,11; 189,73</t>
+          <t>-29,64; 178,86</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>-19,71; 182,38</t>
+          <t>-18,18; 194,7</t>
         </is>
       </c>
     </row>
@@ -1282,7 +1282,7 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>2,33</t>
+          <t>1,39</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
@@ -1297,7 +1297,7 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>-2,02</t>
+          <t>-1,43</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
@@ -1312,7 +1312,7 @@
       </c>
       <c r="K16" s="2" t="inlineStr">
         <is>
-          <t>0,45</t>
+          <t>0,11</t>
         </is>
       </c>
     </row>
@@ -1325,47 +1325,47 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>-6,06; 24,88</t>
+          <t>-4,46; 25,5</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>1,25; 35,89</t>
+          <t>1,16; 35,52</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>-11,97; 17,68</t>
+          <t>-14,91; 15,4</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>-12,3; 12,51</t>
+          <t>-12,75; 13,91</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>-14,13; 13,15</t>
+          <t>-11,92; 16,3</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>-15,19; 10,71</t>
+          <t>-14,61; 10,55</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>-5,85; 14,53</t>
+          <t>-5,11; 14,14</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>-2,83; 19,32</t>
+          <t>-2,16; 19,47</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>-10,13; 10,43</t>
+          <t>-10,3; 9,51</t>
         </is>
       </c>
     </row>
@@ -1388,7 +1388,7 @@
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>10,81%</t>
+          <t>6,44%</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
@@ -1403,7 +1403,7 @@
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>-10,58%</t>
+          <t>-7,5%</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
@@ -1418,7 +1418,7 @@
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>2,24%</t>
+          <t>0,53%</t>
         </is>
       </c>
     </row>
@@ -1431,47 +1431,47 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>-22,08; 175,84</t>
+          <t>-21,78; 185,21</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>2,71; 251,18</t>
+          <t>-0,81; 279,49</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>-43,1; 121,17</t>
+          <t>-50,01; 106,56</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>-50,06; 111,34</t>
+          <t>-49,17; 115,79</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>-51,98; 100,39</t>
+          <t>-48,39; 159,53</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>-57,6; 95,39</t>
+          <t>-54,51; 94,65</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>-23,35; 95,91</t>
+          <t>-22,09; 94,13</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
         <is>
-          <t>-13,62; 113,63</t>
+          <t>-9,57; 133,32</t>
         </is>
       </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>-41,04; 69,81</t>
+          <t>-39,68; 61,72</t>
         </is>
       </c>
     </row>
@@ -1498,7 +1498,7 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>2,54</t>
+          <t>1,93</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
@@ -1513,7 +1513,7 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>10,75</t>
+          <t>11,5</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
@@ -1528,7 +1528,7 @@
       </c>
       <c r="K20" s="2" t="inlineStr">
         <is>
-          <t>8,49</t>
+          <t>8,58</t>
         </is>
       </c>
     </row>
@@ -1541,47 +1541,47 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>-23,21; 31,97</t>
+          <t>-22,35; 31,08</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>-20,66; 36,57</t>
+          <t>-21,05; 36,31</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>-25,88; 28,3</t>
+          <t>-25,36; 26,24</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>-2,5; 29,71</t>
+          <t>-4,22; 28,76</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>-1,85; 38,54</t>
+          <t>-1,23; 38,4</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>-5,72; 26,27</t>
+          <t>-6,36; 29,16</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>-5,36; 24,84</t>
+          <t>-1,84; 26,11</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
         <is>
-          <t>-1,35; 31,23</t>
+          <t>-1,39; 31,63</t>
         </is>
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>-7,17; 21,33</t>
+          <t>-7,03; 22,43</t>
         </is>
       </c>
     </row>
@@ -1604,7 +1604,7 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>8,53%</t>
+          <t>6,49%</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
@@ -1619,7 +1619,7 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>49,55%</t>
+          <t>53,01%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
@@ -1634,7 +1634,7 @@
       </c>
       <c r="K22" s="2" t="inlineStr">
         <is>
-          <t>35,58%</t>
+          <t>35,97%</t>
         </is>
       </c>
     </row>
@@ -1647,54 +1647,54 @@
       </c>
       <c r="C23" s="2" t="inlineStr">
         <is>
-          <t>-51,47; 263,35</t>
+          <t>-47,49; 286,93</t>
         </is>
       </c>
       <c r="D23" s="2" t="inlineStr">
         <is>
-          <t>-45,61; 319,32</t>
+          <t>-50,48; 258,22</t>
         </is>
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>-54,89; 244,26</t>
+          <t>-53,43; 241,53</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>-10,11; 251,59</t>
+          <t>-15,46; 265,71</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
         <is>
-          <t>-6,36; 343,65</t>
+          <t>-4,23; 325,29</t>
         </is>
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>-21,15; 203,97</t>
+          <t>-21,7; 224,48</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>-17,09; 150,7</t>
+          <t>-6,86; 177,72</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
         <is>
-          <t>-8,74; 199,35</t>
+          <t>-3,55; 212,94</t>
         </is>
       </c>
       <c r="K23" s="2" t="inlineStr">
         <is>
-          <t>-20,61; 130,2</t>
+          <t>-19,73; 139,48</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" s="1" t="inlineStr">
         <is>
-          <t>6.0</t>
+          <t>No ha trabajado</t>
         </is>
       </c>
       <c r="B24" s="3" t="inlineStr">
@@ -1714,7 +1714,7 @@
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>-6,3</t>
+          <t>-12,17</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
@@ -1729,7 +1729,7 @@
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>-0,06</t>
+          <t>0,09</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
@@ -1744,7 +1744,7 @@
       </c>
       <c r="K24" s="2" t="inlineStr">
         <is>
-          <t>-0,48</t>
+          <t>-0,98</t>
         </is>
       </c>
     </row>
@@ -1757,47 +1757,47 @@
       </c>
       <c r="C25" s="2" t="inlineStr">
         <is>
-          <t>-53,74; 63,38</t>
+          <t>-52,45; 63,6</t>
         </is>
       </c>
       <c r="D25" s="2" t="inlineStr">
         <is>
-          <t>-87,78; 24,62</t>
+          <t>-87,99; 24,44</t>
         </is>
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>-87,03; 56,5</t>
+          <t>-88,05; 33,56</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>-13,42; 13,21</t>
+          <t>-13,37; 12,61</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
         <is>
-          <t>-15,62; 11,51</t>
+          <t>-16,77; 12,51</t>
         </is>
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>-15,63; 20,21</t>
+          <t>-14,96; 20,59</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>-12,24; 11,93</t>
+          <t>-11,29; 14,12</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
         <is>
-          <t>-17,36; 10,35</t>
+          <t>-16,87; 10,11</t>
         </is>
       </c>
       <c r="K25" s="2" t="inlineStr">
         <is>
-          <t>-15,13; 19,83</t>
+          <t>-14,63; 18,69</t>
         </is>
       </c>
     </row>
@@ -1820,7 +1820,7 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>-25,86%</t>
+          <t>-49,95%</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
@@ -1835,7 +1835,7 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>-0,24%</t>
+          <t>0,35%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
@@ -1850,7 +1850,7 @@
       </c>
       <c r="K26" s="2" t="inlineStr">
         <is>
-          <t>-1,95%</t>
+          <t>-4,0%</t>
         </is>
       </c>
     </row>
@@ -1878,32 +1878,32 @@
       </c>
       <c r="F27" s="2" t="inlineStr">
         <is>
-          <t>-43,82; 72,79</t>
+          <t>-47,04; 71,59</t>
         </is>
       </c>
       <c r="G27" s="2" t="inlineStr">
         <is>
-          <t>-56,45; 62,16</t>
+          <t>-55,9; 78,13</t>
         </is>
       </c>
       <c r="H27" s="2" t="inlineStr">
         <is>
-          <t>-55,3; 115,67</t>
+          <t>-53,24; 113,12</t>
         </is>
       </c>
       <c r="I27" s="2" t="inlineStr">
         <is>
-          <t>-41,22; 63,59</t>
+          <t>-37,97; 85,33</t>
         </is>
       </c>
       <c r="J27" s="2" t="inlineStr">
         <is>
-          <t>-57,94; 56,42</t>
+          <t>-56,06; 58,11</t>
         </is>
       </c>
       <c r="K27" s="2" t="inlineStr">
         <is>
-          <t>-54,24; 105,78</t>
+          <t>-50,98; 120,49</t>
         </is>
       </c>
     </row>
@@ -1930,7 +1930,7 @@
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>7,0</t>
+          <t>7,13</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
@@ -1945,7 +1945,7 @@
       </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
-          <t>2,56</t>
+          <t>2,95</t>
         </is>
       </c>
       <c r="I28" s="2" t="inlineStr">
@@ -1960,7 +1960,7 @@
       </c>
       <c r="K28" s="2" t="inlineStr">
         <is>
-          <t>5,38</t>
+          <t>5,55</t>
         </is>
       </c>
     </row>
@@ -1973,47 +1973,47 @@
       </c>
       <c r="C29" s="2" t="inlineStr">
         <is>
-          <t>-5,58; 14,02</t>
+          <t>-6,49; 13,22</t>
         </is>
       </c>
       <c r="D29" s="2" t="inlineStr">
         <is>
-          <t>-3,07; 17,54</t>
+          <t>-2,92; 18,37</t>
         </is>
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>-4,21; 16,82</t>
+          <t>-2,88; 16,89</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>-3,3; 11,05</t>
+          <t>-2,41; 11,51</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
         <is>
-          <t>-3,43; 12,17</t>
+          <t>-3,2; 12,1</t>
         </is>
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>-4,53; 10,06</t>
+          <t>-3,61; 9,92</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>-2,01; 10,3</t>
+          <t>-1,34; 9,96</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
         <is>
-          <t>-0,33; 11,75</t>
+          <t>-0,07; 12,17</t>
         </is>
       </c>
       <c r="K29" s="2" t="inlineStr">
         <is>
-          <t>-0,61; 11,7</t>
+          <t>-0,3; 11,67</t>
         </is>
       </c>
     </row>
@@ -2036,7 +2036,7 @@
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>26,66%</t>
+          <t>27,15%</t>
         </is>
       </c>
       <c r="F30" s="2" t="inlineStr">
@@ -2051,7 +2051,7 @@
       </c>
       <c r="H30" s="2" t="inlineStr">
         <is>
-          <t>12,68%</t>
+          <t>14,59%</t>
         </is>
       </c>
       <c r="I30" s="2" t="inlineStr">
@@ -2066,7 +2066,7 @@
       </c>
       <c r="K30" s="2" t="inlineStr">
         <is>
-          <t>24,1%</t>
+          <t>24,86%</t>
         </is>
       </c>
     </row>
@@ -2079,47 +2079,47 @@
       </c>
       <c r="C31" s="2" t="inlineStr">
         <is>
-          <t>-19,47; 68,31</t>
+          <t>-20,39; 62,89</t>
         </is>
       </c>
       <c r="D31" s="2" t="inlineStr">
         <is>
-          <t>-9,57; 86,94</t>
+          <t>-11,49; 83,04</t>
         </is>
       </c>
       <c r="E31" s="2" t="inlineStr">
         <is>
-          <t>-14,42; 85,47</t>
+          <t>-9,1; 82,06</t>
         </is>
       </c>
       <c r="F31" s="2" t="inlineStr">
         <is>
-          <t>-13,55; 65,91</t>
+          <t>-10,51; 69,22</t>
         </is>
       </c>
       <c r="G31" s="2" t="inlineStr">
         <is>
-          <t>-15,11; 75,03</t>
+          <t>-14,13; 72,99</t>
         </is>
       </c>
       <c r="H31" s="2" t="inlineStr">
         <is>
-          <t>-18,14; 60,03</t>
+          <t>-16,15; 58,88</t>
         </is>
       </c>
       <c r="I31" s="2" t="inlineStr">
         <is>
-          <t>-7,69; 50,51</t>
+          <t>-4,0; 53,55</t>
         </is>
       </c>
       <c r="J31" s="2" t="inlineStr">
         <is>
-          <t>-0,99; 61,44</t>
+          <t>-0,56; 63,27</t>
         </is>
       </c>
       <c r="K31" s="2" t="inlineStr">
         <is>
-          <t>-2,24; 62,54</t>
+          <t>-1,31; 60,38</t>
         </is>
       </c>
     </row>
